--- a/docs/sheets/Essentials_Remix_AI_Battles.xlsx
+++ b/docs/sheets/Essentials_Remix_AI_Battles.xlsx
@@ -834,7 +834,8 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Run: python3 tools/generate_battle_docs.py — then re-import the .xlsx into Google Sheets.</t>
+          <t>python3 tools/sync_google_sheets.py  (live Google Sheet)
+python3 tools/generate_battle_docs.py  (local .xlsx only)</t>
         </is>
       </c>
     </row>
